--- a/Deliverables/BOM/Sensor-Board/LCSC_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/LCSC_BOM-Sensor-Board.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE8411F-4049-465B-86C7-F8DBE82A244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6498A2F-25C4-49EC-999B-A993804E0029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5685" yWindow="3795" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="840" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="114">
   <si>
     <t>Component list</t>
   </si>
@@ -982,7 +982,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1242,6 +1242,15 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1274,19 +1283,13 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1657,8 +1660,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="104"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1674,15 +1677,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="96"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="99"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1706,7 +1709,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="93"/>
+      <c r="R3" s="96"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1730,7 +1733,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="94"/>
+      <c r="R4" s="97"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1754,7 +1757,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="94"/>
+      <c r="R5" s="97"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1774,7 +1777,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="94"/>
+      <c r="R6" s="97"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1794,7 +1797,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="94"/>
+      <c r="R7" s="97"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1814,7 +1817,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="94"/>
+      <c r="R8" s="97"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2624,25 +2627,25 @@
         <v>5</v>
       </c>
       <c r="D24" s="44"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="97" t="s">
+      <c r="E24" s="102"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="N24" s="98"/>
-      <c r="O24" s="98"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="101"/>
       <c r="P24" s="89">
         <f>SUM(P10:P23)</f>
         <v>259.12919999999997</v>
       </c>
-      <c r="Q24" s="99"/>
-      <c r="R24" s="100"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="103"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2651,25 +2654,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="101"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="97" t="s">
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="98"/>
-      <c r="O25" s="98"/>
+      <c r="N25" s="101"/>
+      <c r="O25" s="101"/>
       <c r="P25" s="90">
         <f>P24/5</f>
         <v>51.825839999999992</v>
       </c>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="102"/>
+      <c r="Q25" s="104"/>
+      <c r="R25" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2704,7 +2707,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6E9644-E7CD-40DF-9083-45958A0FEBB1}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -2732,7 +2735,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="40">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2740,10 +2743,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" s="31">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2751,10 +2754,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C5" s="30">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2762,10 +2765,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C6" s="31">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2773,10 +2776,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="30">
-        <v>6</v>
+        <v>108</v>
+      </c>
+      <c r="C7" s="106">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2784,86 +2787,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C8" s="31">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="74">
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="93">
         <v>7</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="74">
-        <v>8</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="30">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="74">
-        <v>9</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="74">
-        <v>10</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="74">
-        <v>11</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="31">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="74">
-        <v>12</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="105">
-        <v>13</v>
-      </c>
-      <c r="B15" s="106" t="s">
+      <c r="B9" s="107" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="107">
+      <c r="C9" s="108">
         <v>6</v>
       </c>
     </row>

--- a/Deliverables/BOM/Sensor-Board/LCSC_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/LCSC_BOM-Sensor-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6498A2F-25C4-49EC-999B-A993804E0029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A0D5D4-20FF-4787-92E2-08FC0B66C53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="840" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="840" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="117">
   <si>
     <t>Component list</t>
   </si>
@@ -373,6 +373,15 @@
   </si>
   <si>
     <t>C76703</t>
+  </si>
+  <si>
+    <t>C262570</t>
+  </si>
+  <si>
+    <t>C60490</t>
+  </si>
+  <si>
+    <t>C2845290</t>
   </si>
 </sst>
 </file>
@@ -396,6 +405,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1245,6 +1255,15 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1281,15 +1300,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1660,8 +1670,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="98"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1677,15 +1687,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="99"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="102"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1709,7 +1719,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="96"/>
+      <c r="R3" s="99"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1733,7 +1743,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="97"/>
+      <c r="R4" s="100"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1757,7 +1767,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="97"/>
+      <c r="R5" s="100"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1777,7 +1787,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="97"/>
+      <c r="R6" s="100"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1797,7 +1807,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="97"/>
+      <c r="R7" s="100"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1817,7 +1827,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="97"/>
+      <c r="R8" s="100"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2627,25 +2637,25 @@
         <v>5</v>
       </c>
       <c r="D24" s="44"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="103"/>
-      <c r="M24" s="100" t="s">
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="N24" s="101"/>
-      <c r="O24" s="101"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="104"/>
       <c r="P24" s="89">
         <f>SUM(P10:P23)</f>
         <v>259.12919999999997</v>
       </c>
-      <c r="Q24" s="102"/>
-      <c r="R24" s="103"/>
+      <c r="Q24" s="105"/>
+      <c r="R24" s="106"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2654,25 +2664,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="100" t="s">
+      <c r="E25" s="107"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="101"/>
-      <c r="O25" s="101"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
       <c r="P25" s="90">
         <f>P24/5</f>
         <v>51.825839999999992</v>
       </c>
-      <c r="Q25" s="104"/>
-      <c r="R25" s="105"/>
+      <c r="Q25" s="107"/>
+      <c r="R25" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2707,101 +2717,125 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6E9644-E7CD-40DF-9083-45958A0FEBB1}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="C3:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+    <row r="3" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="D4" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="74">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="74">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="D5" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="40">
+      <c r="E5" s="40">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="74">
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="74">
         <v>2</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="D6" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="31">
+      <c r="E6" s="31">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="74">
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="74">
         <v>3</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="30">
+      <c r="D7" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="30">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="74">
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="74">
         <v>4</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="D8" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="31">
+      <c r="E8" s="31">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="74">
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="74">
         <v>5</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="D9" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="94">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="74">
+        <v>6</v>
+      </c>
+      <c r="D10" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="106">
+      <c r="E10" s="31">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="74">
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="74">
+        <v>7</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="94">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="74">
+        <v>8</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="31">
         <v>6</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="31">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="93">
-        <v>7</v>
-      </c>
-      <c r="B9" s="107" t="s">
+    </row>
+    <row r="13" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="93">
+        <v>9</v>
+      </c>
+      <c r="D13" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="108">
-        <v>6</v>
+      <c r="E13" s="96">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Deliverables/BOM/Sensor-Board/LCSC_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/LCSC_BOM-Sensor-Board.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25501"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A0D5D4-20FF-4787-92E2-08FC0B66C53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D04263D-F37F-4309-8FDE-864EDACD8B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="840" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -994,20 +994,20 @@
   </cellStyleXfs>
   <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1017,18 +1017,18 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1043,7 +1043,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1053,7 +1053,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1083,8 +1083,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1096,15 +1096,15 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1640,27 +1640,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" customWidth="1"/>
+    <col min="6" max="6" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="2"/>
@@ -1673,7 +1673,7 @@
       <c r="J1" s="97"/>
       <c r="K1" s="98"/>
     </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="10" t="s">
@@ -1697,7 +1697,7 @@
       <c r="Q2" s="101"/>
       <c r="R2" s="102"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="12" t="s">
@@ -1721,7 +1721,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="99"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="12" t="s">
@@ -1745,7 +1745,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="100"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="12" t="s">
@@ -1769,7 +1769,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="100"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="15"/>
@@ -1789,7 +1789,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="100"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="17"/>
@@ -1809,7 +1809,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="100"/>
     </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="36"/>
       <c r="C8" s="37"/>
@@ -1829,7 +1829,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="100"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="33" t="s">
         <v>4</v>
@@ -1883,7 +1883,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="74">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1936,7 +1936,7 @@
       <c r="Q10" s="53"/>
       <c r="R10" s="48"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="75">
         <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1989,7 +1989,7 @@
       <c r="Q11" s="54"/>
       <c r="R11" s="49"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="75">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2042,7 +2042,7 @@
       <c r="Q12" s="55"/>
       <c r="R12" s="50"/>
     </row>
-    <row r="13" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="75">
         <f t="shared" si="0"/>
@@ -2095,7 +2095,7 @@
       <c r="Q13" s="54"/>
       <c r="R13" s="49"/>
     </row>
-    <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="75">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2148,7 +2148,7 @@
       <c r="Q14" s="55"/>
       <c r="R14" s="50"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="75">
         <f t="shared" si="0"/>
@@ -2201,7 +2201,7 @@
       <c r="Q15" s="54"/>
       <c r="R15" s="49"/>
     </row>
-    <row r="16" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="75">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -2257,7 +2257,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="75">
         <f t="shared" si="0"/>
@@ -2310,7 +2310,7 @@
       <c r="Q17" s="54"/>
       <c r="R17" s="49"/>
     </row>
-    <row r="18" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="69" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="75">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -2363,7 +2363,7 @@
       <c r="Q18" s="55"/>
       <c r="R18" s="50"/>
     </row>
-    <row r="19" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="75">
         <f t="shared" si="0"/>
@@ -2416,7 +2416,7 @@
       <c r="Q19" s="54"/>
       <c r="R19" s="49"/>
     </row>
-    <row r="20" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="75">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -2469,7 +2469,7 @@
       <c r="Q20" s="55"/>
       <c r="R20" s="50"/>
     </row>
-    <row r="21" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="75">
         <f t="shared" si="0"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="R21" s="49"/>
     </row>
-    <row r="22" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="75">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -2577,7 +2577,7 @@
       <c r="Q22" s="55"/>
       <c r="R22" s="50"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="76">
         <f t="shared" si="0"/>
@@ -2630,7 +2630,7 @@
       <c r="Q23" s="57"/>
       <c r="R23" s="52"/>
     </row>
-    <row r="24" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
@@ -2657,7 +2657,7 @@
       <c r="Q24" s="105"/>
       <c r="R24" s="106"/>
     </row>
-    <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="24"/>
       <c r="C25" s="8" t="s">
@@ -2717,124 +2717,121 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6E9644-E7CD-40DF-9083-45958A0FEBB1}">
-  <dimension ref="C3:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="33" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="B1" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="C1" s="33" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="74">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="74">
         <v>1</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="B2" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="E5" s="40">
+      <c r="C2" s="40">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="74">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="74">
         <v>2</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="B3" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="31">
+      <c r="C3" s="31">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="74">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="74">
         <v>3</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="B4" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="30">
+      <c r="C4" s="30">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="74">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="74">
         <v>4</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="B5" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="31">
+      <c r="C5" s="31">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="74">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="74">
         <v>5</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="B6" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="94">
+      <c r="C6" s="94">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="74">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="74">
         <v>6</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="B7" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="31">
+      <c r="C7" s="31">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="74">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="74">
         <v>7</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="B8" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="94">
+      <c r="C8" s="94">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="74">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="74">
         <v>8</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="B9" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="31">
+      <c r="C9" s="31">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="93">
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="93">
         <v>9</v>
       </c>
-      <c r="D13" s="95" t="s">
+      <c r="B10" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="96">
+      <c r="C10" s="96">
         <v>11</v>
       </c>
     </row>
